--- a/section9_kinetics/C2/c2_data.xlsx
+++ b/section9_kinetics/C2/c2_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/mayerlab_files/Stefan/Paper2025/raw_data_2025_09_05/C2_propionaldehyde/analysis_2025_09_30_pKa_corr/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stefan/Documents/Publikationen/06:25/WaterHTE-main/section9_kinetics/C2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{882A3324-8366-924D-A192-35DAA4018B28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970F7129-380E-FE4F-8F97-E6B9C82DE658}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4100" yWindow="-21100" windowWidth="38400" windowHeight="19500" xr2:uid="{8373A34E-AD36-EB43-AEBC-2176D0328EE9}"/>
+    <workbookView xWindow="-4100" yWindow="-21000" windowWidth="38400" windowHeight="19500" xr2:uid="{8373A34E-AD36-EB43-AEBC-2176D0328EE9}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -30333,7 +30333,7 @@
         <v>1</v>
       </c>
       <c r="J322">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K322">
         <v>9.2799999999999994</v>
@@ -30422,7 +30422,7 @@
         <v>1</v>
       </c>
       <c r="J323">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K323">
         <v>9.2799999999999994</v>
@@ -30511,7 +30511,7 @@
         <v>1</v>
       </c>
       <c r="J324">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K324">
         <v>9.2799999999999994</v>
@@ -30600,7 +30600,7 @@
         <v>1</v>
       </c>
       <c r="J325">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K325">
         <v>9.2799999999999994</v>
@@ -30689,7 +30689,7 @@
         <v>1</v>
       </c>
       <c r="J326">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K326">
         <v>9.2799999999999994</v>
@@ -30778,7 +30778,7 @@
         <v>1</v>
       </c>
       <c r="J327">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K327">
         <v>9.2799999999999994</v>
@@ -30867,7 +30867,7 @@
         <v>1</v>
       </c>
       <c r="J328">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K328">
         <v>9.2799999999999994</v>
@@ -30956,7 +30956,7 @@
         <v>1</v>
       </c>
       <c r="J329">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K329">
         <v>9.2799999999999994</v>
@@ -31045,7 +31045,7 @@
         <v>1</v>
       </c>
       <c r="J330">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K330">
         <v>9.2799999999999994</v>
@@ -31134,7 +31134,7 @@
         <v>1</v>
       </c>
       <c r="J331">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K331">
         <v>9.2799999999999994</v>
@@ -31223,7 +31223,7 @@
         <v>1</v>
       </c>
       <c r="J332">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K332">
         <v>9.2799999999999994</v>
@@ -31312,7 +31312,7 @@
         <v>1</v>
       </c>
       <c r="J333">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K333">
         <v>9.2799999999999994</v>
@@ -31401,7 +31401,7 @@
         <v>1</v>
       </c>
       <c r="J334">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K334">
         <v>9.2799999999999994</v>
@@ -31490,7 +31490,7 @@
         <v>1</v>
       </c>
       <c r="J335">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K335">
         <v>9.2799999999999994</v>
@@ -31579,7 +31579,7 @@
         <v>1</v>
       </c>
       <c r="J336">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K336">
         <v>9.2799999999999994</v>
@@ -31668,7 +31668,7 @@
         <v>1</v>
       </c>
       <c r="J337">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K337">
         <v>9.2799999999999994</v>
@@ -31757,7 +31757,7 @@
         <v>1</v>
       </c>
       <c r="J338">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K338">
         <v>9.64</v>
@@ -31846,7 +31846,7 @@
         <v>1</v>
       </c>
       <c r="J339">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K339">
         <v>9.64</v>
@@ -31935,7 +31935,7 @@
         <v>1</v>
       </c>
       <c r="J340">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K340">
         <v>9.64</v>
@@ -32024,7 +32024,7 @@
         <v>1</v>
       </c>
       <c r="J341">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K341">
         <v>9.64</v>
@@ -32113,7 +32113,7 @@
         <v>1</v>
       </c>
       <c r="J342">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K342">
         <v>9.64</v>
@@ -32202,7 +32202,7 @@
         <v>1</v>
       </c>
       <c r="J343">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K343">
         <v>9.64</v>
@@ -32291,7 +32291,7 @@
         <v>1</v>
       </c>
       <c r="J344">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K344">
         <v>9.64</v>
@@ -32380,7 +32380,7 @@
         <v>1</v>
       </c>
       <c r="J345">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K345">
         <v>9.64</v>
@@ -32469,7 +32469,7 @@
         <v>1</v>
       </c>
       <c r="J346">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K346">
         <v>9.64</v>
@@ -32558,7 +32558,7 @@
         <v>1</v>
       </c>
       <c r="J347">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K347">
         <v>9.64</v>
@@ -32647,7 +32647,7 @@
         <v>1</v>
       </c>
       <c r="J348">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K348">
         <v>9.64</v>
@@ -32736,7 +32736,7 @@
         <v>1</v>
       </c>
       <c r="J349">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K349">
         <v>9.64</v>
@@ -32825,7 +32825,7 @@
         <v>1</v>
       </c>
       <c r="J350">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K350">
         <v>9.64</v>
@@ -32914,7 +32914,7 @@
         <v>1</v>
       </c>
       <c r="J351">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K351">
         <v>9.64</v>
@@ -33003,7 +33003,7 @@
         <v>1</v>
       </c>
       <c r="J352">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K352">
         <v>9.64</v>
@@ -33092,7 +33092,7 @@
         <v>1</v>
       </c>
       <c r="J353">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K353">
         <v>9.64</v>
@@ -33181,7 +33181,7 @@
         <v>1</v>
       </c>
       <c r="J354">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K354">
         <v>10.119999999999999</v>
@@ -33270,7 +33270,7 @@
         <v>1</v>
       </c>
       <c r="J355">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K355">
         <v>10.119999999999999</v>
@@ -33359,7 +33359,7 @@
         <v>1</v>
       </c>
       <c r="J356">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K356">
         <v>10.119999999999999</v>
@@ -33448,7 +33448,7 @@
         <v>1</v>
       </c>
       <c r="J357">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K357">
         <v>10.119999999999999</v>
@@ -33537,7 +33537,7 @@
         <v>1</v>
       </c>
       <c r="J358">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K358">
         <v>10.119999999999999</v>
@@ -33626,7 +33626,7 @@
         <v>1</v>
       </c>
       <c r="J359">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K359">
         <v>10.119999999999999</v>
@@ -33715,7 +33715,7 @@
         <v>1</v>
       </c>
       <c r="J360">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K360">
         <v>10.119999999999999</v>
@@ -33804,7 +33804,7 @@
         <v>1</v>
       </c>
       <c r="J361">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K361">
         <v>10.119999999999999</v>
@@ -33893,7 +33893,7 @@
         <v>1</v>
       </c>
       <c r="J362">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K362">
         <v>10.119999999999999</v>
@@ -33982,7 +33982,7 @@
         <v>1</v>
       </c>
       <c r="J363">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K363">
         <v>10.119999999999999</v>
@@ -34071,7 +34071,7 @@
         <v>1</v>
       </c>
       <c r="J364">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K364">
         <v>10.119999999999999</v>
@@ -34160,7 +34160,7 @@
         <v>1</v>
       </c>
       <c r="J365">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K365">
         <v>10.119999999999999</v>
@@ -34249,7 +34249,7 @@
         <v>1</v>
       </c>
       <c r="J366">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K366">
         <v>10.119999999999999</v>
@@ -34338,7 +34338,7 @@
         <v>1</v>
       </c>
       <c r="J367">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K367">
         <v>10.119999999999999</v>
@@ -34427,7 +34427,7 @@
         <v>1</v>
       </c>
       <c r="J368">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K368">
         <v>10.119999999999999</v>
@@ -34516,7 +34516,7 @@
         <v>1</v>
       </c>
       <c r="J369">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K369">
         <v>10.119999999999999</v>
@@ -34605,7 +34605,7 @@
         <v>1</v>
       </c>
       <c r="J370">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K370">
         <v>10.44</v>
@@ -34694,7 +34694,7 @@
         <v>1</v>
       </c>
       <c r="J371">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K371">
         <v>10.44</v>
@@ -34783,7 +34783,7 @@
         <v>1</v>
       </c>
       <c r="J372">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K372">
         <v>10.44</v>
@@ -34872,7 +34872,7 @@
         <v>1</v>
       </c>
       <c r="J373">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K373">
         <v>10.44</v>
@@ -34961,7 +34961,7 @@
         <v>1</v>
       </c>
       <c r="J374">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K374">
         <v>10.44</v>
@@ -35050,7 +35050,7 @@
         <v>1</v>
       </c>
       <c r="J375">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K375">
         <v>10.44</v>
@@ -35139,7 +35139,7 @@
         <v>1</v>
       </c>
       <c r="J376">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K376">
         <v>10.44</v>
@@ -35228,7 +35228,7 @@
         <v>1</v>
       </c>
       <c r="J377">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K377">
         <v>10.44</v>
@@ -35317,7 +35317,7 @@
         <v>1</v>
       </c>
       <c r="J378">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K378">
         <v>10.44</v>
@@ -35406,7 +35406,7 @@
         <v>1</v>
       </c>
       <c r="J379">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K379">
         <v>10.44</v>
@@ -35495,7 +35495,7 @@
         <v>1</v>
       </c>
       <c r="J380">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K380">
         <v>10.44</v>
@@ -35584,7 +35584,7 @@
         <v>1</v>
       </c>
       <c r="J381">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K381">
         <v>10.44</v>
@@ -35673,7 +35673,7 @@
         <v>1</v>
       </c>
       <c r="J382">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K382">
         <v>10.44</v>
@@ -35762,7 +35762,7 @@
         <v>1</v>
       </c>
       <c r="J383">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K383">
         <v>10.44</v>
@@ -35851,7 +35851,7 @@
         <v>1</v>
       </c>
       <c r="J384">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K384">
         <v>10.44</v>
@@ -35940,7 +35940,7 @@
         <v>1</v>
       </c>
       <c r="J385">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K385">
         <v>10.44</v>
